--- a/research/traditional_assets/database/data/qatar/qatar_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_banks_regional.xlsx
@@ -587,29 +587,23 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.233</v>
-      </c>
-      <c r="E2">
-        <v>-0.139</v>
-      </c>
       <c r="G2">
-        <v>-0.9217877094972067</v>
+        <v>1.107734806629834</v>
       </c>
       <c r="H2">
-        <v>-0.9217877094972067</v>
+        <v>1.107734806629834</v>
       </c>
       <c r="I2">
-        <v>0.7029622295468321</v>
+        <v>1.001833881426276</v>
       </c>
       <c r="J2">
-        <v>0.7029622295468321</v>
+        <v>1.001833881426276</v>
       </c>
       <c r="K2">
-        <v>17.4</v>
+        <v>28</v>
       </c>
       <c r="L2">
-        <v>0.324022346368715</v>
+        <v>0.7734806629834253</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,73 +627,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>260.6</v>
+        <v>476.8</v>
       </c>
       <c r="V2">
-        <v>0.7571179546775132</v>
+        <v>1.353391995458416</v>
       </c>
       <c r="W2">
-        <v>0.1333333333333333</v>
+        <v>0.187793427230047</v>
       </c>
       <c r="X2">
-        <v>0.04581255033716868</v>
+        <v>0.06395867527591961</v>
       </c>
       <c r="Y2">
-        <v>0.08752078299616466</v>
-      </c>
-      <c r="Z2">
-        <v>-0.3247845864365794</v>
-      </c>
-      <c r="AA2">
-        <v>-0.2283112970039037</v>
+        <v>0.1238347519541274</v>
       </c>
       <c r="AB2">
-        <v>0.045791190850037</v>
-      </c>
-      <c r="AC2">
-        <v>-0.2741024878539406</v>
+        <v>0.06394366052680632</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>0.4596413666755579</v>
+        <v>0.3580674618440526</v>
       </c>
       <c r="AF2">
-        <v>0.4596413666755579</v>
+        <v>0.3580674618440526</v>
       </c>
       <c r="AG2">
-        <v>-260.1403586333245</v>
+        <v>-476.441932538156</v>
       </c>
       <c r="AH2">
-        <v>0.001333609484571348</v>
+        <v>0.001015338921412294</v>
       </c>
       <c r="AI2">
-        <v>0.002983528733405077</v>
+        <v>0.001179956970130889</v>
       </c>
       <c r="AJ2">
-        <v>-3.094711735665983</v>
+        <v>3.837880745023185</v>
       </c>
       <c r="AK2">
-        <v>2.441707179986495</v>
+        <v>2.748567098346395</v>
       </c>
       <c r="AL2">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AM2">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AO2">
-        <v>21.60919540229885</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="AP2">
-        <v>-7.945400526353027</v>
+        <v>-12.96864098584996</v>
       </c>
       <c r="AQ2">
-        <v>21.60919540229885</v>
+        <v>21.81818181818182</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +695,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Qatar First Bank L.L.C (Public) (DSM:QFBQ)</t>
+          <t>Lesha Bank LLC (DSM:QFBQ)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,29 +703,23 @@
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.233</v>
-      </c>
-      <c r="E3">
-        <v>-0.139</v>
-      </c>
       <c r="G3">
-        <v>-0.9217877094972067</v>
+        <v>1.107734806629834</v>
       </c>
       <c r="H3">
-        <v>-0.9217877094972067</v>
+        <v>1.107734806629834</v>
       </c>
       <c r="I3">
-        <v>0.7029622295468321</v>
+        <v>1.001833881426276</v>
       </c>
       <c r="J3">
-        <v>0.7029622295468321</v>
+        <v>1.001833881426276</v>
       </c>
       <c r="K3">
-        <v>17.4</v>
+        <v>28</v>
       </c>
       <c r="L3">
-        <v>0.324022346368715</v>
+        <v>0.7734806629834253</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,73 +743,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>260.6</v>
+        <v>476.8</v>
       </c>
       <c r="V3">
-        <v>0.7571179546775132</v>
+        <v>1.353391995458416</v>
       </c>
       <c r="W3">
-        <v>0.1333333333333333</v>
+        <v>0.187793427230047</v>
       </c>
       <c r="X3">
-        <v>0.04581255033716868</v>
+        <v>0.06395867527591961</v>
       </c>
       <c r="Y3">
-        <v>0.08752078299616466</v>
-      </c>
-      <c r="Z3">
-        <v>-0.3247845864365794</v>
-      </c>
-      <c r="AA3">
-        <v>-0.2283112970039037</v>
+        <v>0.1238347519541274</v>
       </c>
       <c r="AB3">
-        <v>0.045791190850037</v>
-      </c>
-      <c r="AC3">
-        <v>-0.2741024878539406</v>
+        <v>0.06394366052680632</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.4596413666755579</v>
+        <v>0.3580674618440526</v>
       </c>
       <c r="AF3">
-        <v>0.4596413666755579</v>
+        <v>0.3580674618440526</v>
       </c>
       <c r="AG3">
-        <v>-260.1403586333245</v>
+        <v>-476.441932538156</v>
       </c>
       <c r="AH3">
-        <v>0.001333609484571348</v>
+        <v>0.001015338921412294</v>
       </c>
       <c r="AI3">
-        <v>0.002983528733405077</v>
+        <v>0.001179956970130889</v>
       </c>
       <c r="AJ3">
-        <v>-3.094711735665983</v>
+        <v>3.837880745023185</v>
       </c>
       <c r="AK3">
-        <v>2.441707179986495</v>
+        <v>2.748567098346395</v>
       </c>
       <c r="AL3">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AM3">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>21.60919540229885</v>
+        <v>21.81818181818182</v>
       </c>
       <c r="AP3">
-        <v>-7.945400526353027</v>
+        <v>-12.96864098584996</v>
       </c>
       <c r="AQ3">
-        <v>21.60919540229885</v>
+        <v>21.81818181818182</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/qatar/qatar_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,103 +588,109 @@
         </is>
       </c>
       <c r="G2">
-        <v>1.107734806629834</v>
+        <v>0.01285638156141753</v>
       </c>
       <c r="H2">
-        <v>1.107734806629834</v>
+        <v>0.01285638156141753</v>
       </c>
       <c r="I2">
-        <v>1.001833881426276</v>
+        <v>0.01015097515015103</v>
       </c>
       <c r="J2">
-        <v>1.001833881426276</v>
+        <v>0.01014876716152724</v>
       </c>
       <c r="K2">
-        <v>28</v>
+        <v>373.1</v>
       </c>
       <c r="L2">
-        <v>0.7734806629834253</v>
+        <v>0.2485345057287504</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>248.1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04052663388817197</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.664969177164299</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>248.1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04052663388817197</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.664969177164299</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>476.8</v>
+        <v>1008.8</v>
       </c>
       <c r="V2">
-        <v>1.353391995458416</v>
+        <v>0.1647854424280044</v>
       </c>
       <c r="W2">
-        <v>0.187793427230047</v>
+        <v>0.08126602293129036</v>
       </c>
       <c r="X2">
-        <v>0.06395867527591961</v>
+        <v>0.06138126059939938</v>
       </c>
       <c r="Y2">
-        <v>0.1238347519541274</v>
+        <v>0.01988476233189098</v>
+      </c>
+      <c r="Z2">
+        <v>0.2175177171797613</v>
       </c>
       <c r="AB2">
-        <v>0.06394366052680632</v>
+        <v>0.05807680458452341</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>5189.4</v>
       </c>
       <c r="AE2">
-        <v>0.3580674618440526</v>
+        <v>1.8067805229664</v>
       </c>
       <c r="AF2">
-        <v>0.3580674618440526</v>
+        <v>5191.206780522966</v>
       </c>
       <c r="AG2">
-        <v>-476.441932538156</v>
+        <v>4182.406780522966</v>
       </c>
       <c r="AH2">
-        <v>0.001015338921412294</v>
+        <v>0.4588665944053783</v>
       </c>
       <c r="AI2">
-        <v>0.001179956970130889</v>
+        <v>0.5454434070367347</v>
       </c>
       <c r="AJ2">
-        <v>3.837880745023185</v>
+        <v>0.4058891946451443</v>
       </c>
       <c r="AK2">
-        <v>2.748567098346395</v>
+        <v>0.4915501313442884</v>
       </c>
       <c r="AL2">
-        <v>1.65</v>
+        <v>0.507</v>
       </c>
       <c r="AM2">
-        <v>1.65</v>
+        <v>0.507</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>316.4268292682926</v>
       </c>
       <c r="AO2">
-        <v>21.81818181818182</v>
+        <v>27.61341222879684</v>
       </c>
       <c r="AP2">
-        <v>-12.96864098584996</v>
+        <v>255.0248036904247</v>
       </c>
       <c r="AQ2">
-        <v>21.81818181818182</v>
+        <v>27.61341222879684</v>
       </c>
     </row>
     <row r="3">
@@ -704,22 +710,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>1.107734806629834</v>
+        <v>0.5302197802197802</v>
       </c>
       <c r="H3">
-        <v>1.107734806629834</v>
+        <v>0.5302197802197802</v>
       </c>
       <c r="I3">
-        <v>1.001833881426276</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="J3">
-        <v>1.001833881426276</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="K3">
-        <v>28</v>
+        <v>21.6</v>
       </c>
       <c r="L3">
-        <v>0.7734806629834253</v>
+        <v>0.5934065934065935</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,64 +749,186 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>476.8</v>
+        <v>876</v>
       </c>
       <c r="V3">
-        <v>1.353391995458416</v>
+        <v>2.152334152334152</v>
       </c>
       <c r="W3">
-        <v>0.187793427230047</v>
+        <v>0.07042712748614281</v>
       </c>
       <c r="X3">
-        <v>0.06395867527591961</v>
+        <v>0.05482913414965793</v>
       </c>
       <c r="Y3">
-        <v>0.1238347519541274</v>
+        <v>0.01559799333648489</v>
       </c>
       <c r="AB3">
-        <v>0.06394366052680632</v>
+        <v>0.05482913414965793</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.3580674618440526</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.3580674618440526</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-476.441932538156</v>
+        <v>-876</v>
       </c>
       <c r="AH3">
-        <v>0.001015338921412294</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.001179956970130889</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>3.837880745023185</v>
+        <v>1.867803837953092</v>
       </c>
       <c r="AK3">
-        <v>2.748567098346395</v>
+        <v>1.586381745744295</v>
       </c>
       <c r="AL3">
-        <v>1.65</v>
+        <v>0.507</v>
       </c>
       <c r="AM3">
-        <v>1.65</v>
+        <v>0.507</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>21.81818181818182</v>
+        <v>27.61341222879684</v>
       </c>
       <c r="AP3">
-        <v>-12.96864098584996</v>
+        <v>-59.18918918918919</v>
       </c>
       <c r="AQ3">
-        <v>21.81818181818182</v>
+        <v>27.61341222879684</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dukhan Bank Q.P.S.C. (DSM:DUBK)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.0008456061547014747</v>
+      </c>
+      <c r="J4">
+        <v>0.0008452382907786162</v>
+      </c>
+      <c r="K4">
+        <v>351.5</v>
+      </c>
+      <c r="L4">
+        <v>0.2399645002730748</v>
+      </c>
+      <c r="M4">
+        <v>248.1</v>
+      </c>
+      <c r="N4">
+        <v>0.04341283312043955</v>
+      </c>
+      <c r="O4">
+        <v>0.7058321479374111</v>
+      </c>
+      <c r="P4">
+        <v>248.1</v>
+      </c>
+      <c r="Q4">
+        <v>0.04341283312043955</v>
+      </c>
+      <c r="R4">
+        <v>0.7058321479374111</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>132.8</v>
+      </c>
+      <c r="V4">
+        <v>0.02323750196853839</v>
+      </c>
+      <c r="W4">
+        <v>0.0921049183764379</v>
+      </c>
+      <c r="X4">
+        <v>0.06793338704914083</v>
+      </c>
+      <c r="Y4">
+        <v>0.02417153132729707</v>
+      </c>
+      <c r="Z4">
+        <v>0.2122435066113205</v>
+      </c>
+      <c r="AA4">
+        <v>0.0001793963387570125</v>
+      </c>
+      <c r="AB4">
+        <v>0.0613244750193889</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06114507868063188</v>
+      </c>
+      <c r="AD4">
+        <v>5189.4</v>
+      </c>
+      <c r="AE4">
+        <v>1.8067805229664</v>
+      </c>
+      <c r="AF4">
+        <v>5191.206780522966</v>
+      </c>
+      <c r="AG4">
+        <v>5058.406780522966</v>
+      </c>
+      <c r="AH4">
+        <v>0.4759908265150912</v>
+      </c>
+      <c r="AI4">
+        <v>0.5646539931989206</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4695314895950097</v>
+      </c>
+      <c r="AK4">
+        <v>0.5582733307365604</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>3243.375</v>
+      </c>
+      <c r="AP4">
+        <v>3161.504237826854</v>
       </c>
     </row>
   </sheetData>
